--- a/data-manipulation-scripts/sheets-cleanup/sheets/BOMBA ÓLEO - 26_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BOMBA ÓLEO - 26_01.xlsx
@@ -440,7 +440,9 @@
       <c r="C4" s="2">
         <v>2.0</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="2">
+        <v>85.0</v>
+      </c>
       <c r="E4" s="3" t="s">
         <v>7</v>
       </c>
@@ -455,7 +457,9 @@
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="2">
+        <v>60.0</v>
+      </c>
       <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
@@ -521,7 +525,9 @@
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2">
+        <v>82.0</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>7</v>
       </c>
@@ -536,7 +542,9 @@
       <c r="C10" s="2">
         <v>1.0</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="2">
+        <v>82.0</v>
+      </c>
       <c r="E10" s="3" t="s">
         <v>7</v>
       </c>
